--- a/plantillas/consulta/Proyectos_Opinar.xlsx
+++ b/plantillas/consulta/Proyectos_Opinar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D60FEA-4580-4156-967C-793F8D3692F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ED7D1E-4EC1-46F3-9F8B-87C14C4725F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F752A01-72FF-4D34-B180-C2EAD64A4CCD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>titulo 1</t>
   </si>
@@ -44,9 +44,6 @@
     <t>titulo 2</t>
   </si>
   <si>
-    <t>Dirección Distrital:</t>
-  </si>
-  <si>
     <t>Nombre de la Unidad Territorial</t>
   </si>
   <si>
@@ -68,7 +65,8 @@
     <t>No. del Proyecto</t>
   </si>
   <si>
-    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS (SICOVACC)</t>
+    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
+SICOVACC 2026</t>
   </si>
 </sst>
 </file>
@@ -160,21 +158,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -183,10 +175,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,7 +526,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A2:G11"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -540,86 +537,83 @@
     <col min="6" max="6" width="41.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F9" s="1"/>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/plantillas/consulta/Proyectos_Opinar.xlsx
+++ b/plantillas/consulta/Proyectos_Opinar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ED7D1E-4EC1-46F3-9F8B-87C14C4725F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4E71D2-9BEC-4F8B-9CD9-5AB32770F2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F752A01-72FF-4D34-B180-C2EAD64A4CCD}"/>
   </bookViews>
@@ -66,7 +66,7 @@
   </si>
   <si>
     <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
-SICOVACC 2026</t>
+SICOVACC</t>
   </si>
 </sst>
 </file>
@@ -169,6 +169,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -177,12 +183,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,45 +538,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
@@ -587,12 +587,12 @@
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="F8" s="8"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F9" s="8"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
